--- a/Data protest_online.xlsx
+++ b/Data protest_online.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6770" tabRatio="376"/>
+    <workbookView windowWidth="18350" windowHeight="6680" tabRatio="376"/>
   </bookViews>
   <sheets>
     <sheet name="Онлайн-опитування протестуючих" sheetId="1" r:id="rId1"/>
@@ -282,7 +282,7 @@
     <t>А наскільки Ви впевнені у тому, що можете впливати на рішення влади?</t>
   </si>
   <si>
-    <t>Наскільки закон №12414 викликає занепокоєння особисто у Вас? []</t>
+    <t>Наскільки закон №12414 викликає занепокоєння особисто у Вас?</t>
   </si>
   <si>
     <t>Які саме його положення викликають у Вас занепокоєння?</t>
@@ -1805,6 +1805,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Масив містить змінну </t>
     </r>
     <r>
@@ -2464,7 +2470,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2494,9 +2500,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2508,9 +2511,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4264,7 +4264,7 @@
     <tableColumn id="81" name="У яких попередніх великих протестах в Україні брав участь хтось з Ваших батьків? [Не знаю]" dataDxfId="80"/>
     <tableColumn id="82" name="Наскільки, на Вашу думку, нинішня політична система в Україні дає змогу звичайним людям впливати на рішення влади?" dataDxfId="81"/>
     <tableColumn id="83" name="А наскільки Ви впевнені у тому, що можете впливати на рішення влади?" dataDxfId="82"/>
-    <tableColumn id="84" name="Наскільки закон №12414 викликає занепокоєння особисто у Вас? []" dataDxfId="83"/>
+    <tableColumn id="84" name="Наскільки закон №12414 викликає занепокоєння особисто у Вас?" dataDxfId="83"/>
     <tableColumn id="85" name="Які саме його положення викликають у Вас занепокоєння?" dataDxfId="84"/>
   </tableColumns>
   <tableStyleInfo name="TableStylePreset3_Dark" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4658,7 +4658,7 @@
       <c r="W1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="X1" s="10" t="s">
         <v>23</v>
       </c>
       <c r="Y1" s="7" t="s">
@@ -4751,7 +4751,7 @@
       <c r="BB1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="16" t="s">
+      <c r="BC1" s="2" t="s">
         <v>54</v>
       </c>
       <c r="BD1" s="7" t="s">
@@ -4907,32 +4907,32 @@
       <c r="U2" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V2" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z2" s="14" t="s">
+      <c r="V2" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z2" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA2" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB2" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC2" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD2" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE2" s="15" t="s">
+      <c r="AA2" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB2" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC2" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD2" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE2" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF2" s="8" t="s">
@@ -4950,22 +4950,22 @@
       <c r="AJ2" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK2" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL2" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM2" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN2" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO2" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP2" s="12" t="s">
+      <c r="AK2" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL2" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM2" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN2" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO2" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP2" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ2" s="8" t="s">
@@ -5156,32 +5156,32 @@
       <c r="U3" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V3" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W3" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z3" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA3" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB3" s="14" t="s">
+      <c r="V3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X3" s="12"/>
+      <c r="Y3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB3" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC3" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD3" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE3" s="15" t="s">
+      <c r="AC3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD3" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE3" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF3" s="8" t="s">
@@ -5199,22 +5199,22 @@
       <c r="AJ3" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK3" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL3" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM3" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN3" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO3" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP3" s="12" t="s">
+      <c r="AK3" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL3" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM3" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN3" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP3" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ3" s="8" t="s">
@@ -5403,32 +5403,32 @@
       <c r="U4" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V4" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W4" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="14" t="s">
+      <c r="V4" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W4" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z4" s="14" t="s">
+      <c r="Z4" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA4" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB4" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC4" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD4" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE4" s="15" t="s">
+      <c r="AA4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD4" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE4" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF4" s="8" t="s">
@@ -5446,22 +5446,22 @@
       <c r="AJ4" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK4" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL4" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM4" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN4" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO4" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP4" s="12" t="s">
+      <c r="AK4" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL4" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM4" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN4" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO4" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP4" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ4" s="8" t="s">
@@ -5652,32 +5652,32 @@
       <c r="U5" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V5" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W5" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z5" s="14" t="s">
+      <c r="V5" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z5" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA5" s="14" t="s">
+      <c r="AA5" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB5" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC5" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD5" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE5" s="15" t="s">
+      <c r="AB5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD5" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE5" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF5" s="8" t="s">
@@ -5695,22 +5695,22 @@
       <c r="AJ5" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK5" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL5" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM5" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN5" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO5" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP5" s="12" t="s">
+      <c r="AK5" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL5" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM5" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP5" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ5" s="8" t="s">
@@ -5901,32 +5901,32 @@
       <c r="U6" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V6" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W6" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z6" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA6" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB6" s="14" t="s">
+      <c r="V6" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB6" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC6" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD6" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE6" s="15" t="s">
+      <c r="AC6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD6" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE6" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF6" s="8" t="s">
@@ -5944,22 +5944,22 @@
       <c r="AJ6" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK6" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL6" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO6" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP6" s="12" t="s">
+      <c r="AK6" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL6" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO6" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP6" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ6" s="8" t="s">
@@ -6150,32 +6150,32 @@
       <c r="U7" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V7" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="14" t="s">
+      <c r="V7" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z7" s="14" t="s">
+      <c r="Z7" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA7" s="14" t="s">
+      <c r="AA7" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB7" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC7" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD7" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE7" s="15" t="s">
+      <c r="AB7" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC7" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD7" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE7" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF7" s="8" t="s">
@@ -6193,22 +6193,22 @@
       <c r="AJ7" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK7" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL7" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM7" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN7" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO7" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP7" s="12" t="s">
+      <c r="AK7" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL7" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM7" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN7" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO7" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP7" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ7" s="8" t="s">
@@ -6403,32 +6403,32 @@
       <c r="U8" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V8" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W8" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z8" s="14" t="s">
+      <c r="V8" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W8" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z8" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA8" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB8" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC8" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD8" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE8" s="15" t="s">
+      <c r="AA8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD8" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE8" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF8" s="8" t="s">
@@ -6446,22 +6446,22 @@
       <c r="AJ8" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK8" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL8" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM8" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN8" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO8" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP8" s="12" t="s">
+      <c r="AK8" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL8" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM8" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN8" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO8" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP8" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ8" s="8" t="s">
@@ -6650,32 +6650,32 @@
       <c r="U9" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V9" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W9" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z9" s="14" t="s">
+      <c r="V9" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W9" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z9" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA9" s="14" t="s">
+      <c r="AA9" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB9" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC9" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD9" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE9" s="15" t="s">
+      <c r="AB9" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC9" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD9" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE9" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF9" s="8" t="s">
@@ -6693,22 +6693,22 @@
       <c r="AJ9" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK9" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL9" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM9" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN9" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO9" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP9" s="12" t="s">
+      <c r="AK9" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL9" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM9" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN9" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO9" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP9" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ9" s="8" t="s">
@@ -6895,32 +6895,32 @@
       <c r="U10" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V10" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W10" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="14" t="s">
+      <c r="V10" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W10" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z10" s="14" t="s">
+      <c r="Z10" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA10" s="14" t="s">
+      <c r="AA10" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB10" s="14" t="s">
+      <c r="AB10" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC10" s="14" t="s">
+      <c r="AC10" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD10" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE10" s="15" t="s">
+      <c r="AD10" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE10" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF10" s="8">
@@ -6938,22 +6938,22 @@
       <c r="AJ10" s="8">
         <v>3</v>
       </c>
-      <c r="AK10" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL10" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM10" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN10" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO10" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP10" s="12" t="s">
+      <c r="AK10" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL10" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM10" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN10" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO10" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP10" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ10" s="8" t="s">
@@ -7148,32 +7148,32 @@
       <c r="U11" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V11" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W11" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="14" t="s">
+      <c r="V11" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W11" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z11" s="14" t="s">
+      <c r="Z11" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA11" s="14" t="s">
+      <c r="AA11" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB11" s="14" t="s">
+      <c r="AB11" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AC11" s="14" t="s">
+      <c r="AC11" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AD11" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE11" s="15" t="s">
+      <c r="AD11" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE11" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF11" s="8">
@@ -7191,22 +7191,22 @@
       <c r="AJ11" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK11" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL11" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM11" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN11" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO11" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP11" s="12" t="s">
+      <c r="AK11" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL11" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM11" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN11" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO11" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP11" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ11" s="8" t="s">
@@ -7397,32 +7397,32 @@
       <c r="U12" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V12" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W12" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="14" t="s">
+      <c r="V12" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W12" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z12" s="14" t="s">
+      <c r="Z12" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA12" s="14" t="s">
+      <c r="AA12" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB12" s="14" t="s">
+      <c r="AB12" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AC12" s="14" t="s">
+      <c r="AC12" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AD12" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE12" s="15" t="s">
+      <c r="AD12" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE12" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF12" s="8">
@@ -7440,22 +7440,22 @@
       <c r="AJ12" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK12" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL12" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM12" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN12" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO12" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP12" s="12" t="s">
+      <c r="AK12" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL12" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM12" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN12" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO12" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP12" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ12" s="8" t="s">
@@ -7646,32 +7646,32 @@
       <c r="U13" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V13" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W13" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z13" s="14" t="s">
+      <c r="V13" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W13" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z13" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA13" s="14" t="s">
+      <c r="AA13" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB13" s="14" t="s">
+      <c r="AB13" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AC13" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD13" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE13" s="15" t="s">
+      <c r="AC13" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD13" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE13" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF13" s="8" t="s">
@@ -7689,22 +7689,22 @@
       <c r="AJ13" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK13" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL13" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM13" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN13" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO13" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP13" s="12" t="s">
+      <c r="AK13" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL13" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM13" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN13" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO13" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP13" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ13" s="8" t="s">
@@ -7895,32 +7895,32 @@
       <c r="U14" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V14" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W14" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X14" s="13"/>
-      <c r="Y14" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z14" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA14" s="14" t="s">
+      <c r="V14" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W14" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z14" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA14" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB14" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC14" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD14" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE14" s="15" t="s">
+      <c r="AB14" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC14" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD14" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE14" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF14" s="8" t="s">
@@ -7938,22 +7938,22 @@
       <c r="AJ14" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK14" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL14" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM14" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN14" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO14" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP14" s="12" t="s">
+      <c r="AK14" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL14" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM14" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN14" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO14" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP14" s="11" t="s">
         <v>85</v>
       </c>
       <c r="AQ14" s="8" t="s">
@@ -8138,32 +8138,32 @@
       <c r="U15" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V15" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W15" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="14" t="s">
+      <c r="V15" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W15" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z15" s="14" t="s">
+      <c r="Z15" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA15" s="14" t="s">
+      <c r="AA15" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB15" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC15" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD15" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE15" s="15" t="s">
+      <c r="AB15" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC15" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD15" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE15" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF15" s="8">
@@ -8181,22 +8181,22 @@
       <c r="AJ15" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK15" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL15" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM15" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN15" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO15" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP15" s="12" t="s">
+      <c r="AK15" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL15" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM15" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN15" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO15" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP15" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ15" s="8" t="s">
@@ -8385,32 +8385,32 @@
       <c r="U16" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V16" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W16" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X16" s="13"/>
-      <c r="Y16" s="14" t="s">
+      <c r="V16" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W16" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z16" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA16" s="14" t="s">
+      <c r="Z16" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA16" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB16" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC16" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD16" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE16" s="15" t="s">
+      <c r="AB16" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC16" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD16" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE16" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF16" s="8">
@@ -8428,22 +8428,22 @@
       <c r="AJ16" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK16" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL16" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM16" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN16" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO16" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP16" s="12" t="s">
+      <c r="AK16" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL16" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM16" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN16" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO16" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP16" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ16" s="8" t="s">
@@ -8634,32 +8634,32 @@
       <c r="U17" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V17" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W17" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z17" s="14" t="s">
+      <c r="V17" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W17" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z17" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA17" s="14" t="s">
+      <c r="AA17" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB17" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC17" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD17" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE17" s="15" t="s">
+      <c r="AB17" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC17" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD17" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE17" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF17" s="8" t="s">
@@ -8677,22 +8677,22 @@
       <c r="AJ17" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK17" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL17" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM17" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN17" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO17" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP17" s="12" t="s">
+      <c r="AK17" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL17" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM17" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN17" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO17" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP17" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ17" s="8" t="s">
@@ -8883,32 +8883,32 @@
       <c r="U18" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V18" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W18" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X18" s="13"/>
-      <c r="Y18" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z18" s="14" t="s">
+      <c r="V18" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W18" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z18" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA18" s="14" t="s">
+      <c r="AA18" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB18" s="14" t="s">
+      <c r="AB18" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC18" s="14" t="s">
+      <c r="AC18" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD18" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE18" s="15" t="s">
+      <c r="AD18" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE18" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF18" s="8" t="s">
@@ -8926,22 +8926,22 @@
       <c r="AJ18" s="8">
         <v>4</v>
       </c>
-      <c r="AK18" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL18" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM18" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN18" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO18" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP18" s="12" t="s">
+      <c r="AK18" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL18" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM18" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN18" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO18" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP18" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ18" s="8" t="s">
@@ -9128,32 +9128,32 @@
       <c r="U19" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V19" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W19" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z19" s="14" t="s">
+      <c r="V19" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W19" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z19" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA19" s="14" t="s">
+      <c r="AA19" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB19" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC19" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD19" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE19" s="15" t="s">
+      <c r="AB19" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC19" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD19" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE19" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF19" s="8" t="s">
@@ -9171,22 +9171,22 @@
       <c r="AJ19" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK19" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL19" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM19" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN19" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO19" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP19" s="12" t="s">
+      <c r="AK19" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL19" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM19" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN19" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO19" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP19" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ19" s="8" t="s">
@@ -9375,32 +9375,32 @@
       <c r="U20" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V20" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W20" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X20" s="13"/>
-      <c r="Y20" s="14" t="s">
+      <c r="V20" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W20" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z20" s="14" t="s">
+      <c r="Z20" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA20" s="14" t="s">
+      <c r="AA20" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB20" s="14" t="s">
+      <c r="AB20" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AC20" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD20" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE20" s="15" t="s">
+      <c r="AC20" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD20" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE20" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF20" s="8" t="s">
@@ -9418,22 +9418,22 @@
       <c r="AJ20" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK20" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL20" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM20" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN20" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO20" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP20" s="12" t="s">
+      <c r="AK20" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL20" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM20" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN20" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO20" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP20" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ20" s="8" t="s">
@@ -9624,32 +9624,32 @@
       <c r="U21" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V21" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W21" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X21" s="13"/>
-      <c r="Y21" s="14" t="s">
+      <c r="V21" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W21" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z21" s="14" t="s">
+      <c r="Z21" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA21" s="14" t="s">
+      <c r="AA21" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB21" s="14" t="s">
+      <c r="AB21" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC21" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD21" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE21" s="15" t="s">
+      <c r="AC21" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD21" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE21" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF21" s="8" t="s">
@@ -9667,22 +9667,22 @@
       <c r="AJ21" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK21" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL21" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM21" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN21" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO21" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP21" s="12" t="s">
+      <c r="AK21" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL21" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM21" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN21" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO21" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP21" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ21" s="8" t="s">
@@ -9867,32 +9867,32 @@
       <c r="U22" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V22" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W22" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X22" s="13"/>
-      <c r="Y22" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z22" s="14" t="s">
+      <c r="V22" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W22" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z22" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA22" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB22" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC22" s="14" t="s">
+      <c r="AA22" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB22" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC22" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD22" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE22" s="15" t="s">
+      <c r="AD22" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE22" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF22" s="8" t="s">
@@ -9910,22 +9910,22 @@
       <c r="AJ22" s="8">
         <v>7</v>
       </c>
-      <c r="AK22" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL22" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM22" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN22" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO22" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP22" s="12" t="s">
+      <c r="AK22" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL22" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM22" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN22" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO22" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP22" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ22" s="8" t="s">
@@ -10118,32 +10118,32 @@
       <c r="U23" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V23" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W23" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X23" s="13"/>
-      <c r="Y23" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z23" s="14" t="s">
+      <c r="V23" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W23" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z23" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA23" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB23" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC23" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD23" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE23" s="15" t="s">
+      <c r="AA23" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB23" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC23" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD23" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE23" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF23" s="8" t="s">
@@ -10161,22 +10161,22 @@
       <c r="AJ23" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK23" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL23" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM23" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN23" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO23" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP23" s="12" t="s">
+      <c r="AK23" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL23" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM23" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN23" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO23" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP23" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ23" s="8" t="s">
@@ -10369,32 +10369,32 @@
       <c r="U24" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V24" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W24" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X24" s="13"/>
-      <c r="Y24" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z24" s="14" t="s">
+      <c r="V24" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W24" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z24" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA24" s="14" t="s">
+      <c r="AA24" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB24" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC24" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD24" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE24" s="15" t="s">
+      <c r="AB24" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC24" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD24" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE24" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF24" s="8" t="s">
@@ -10412,22 +10412,22 @@
       <c r="AJ24" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK24" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL24" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM24" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN24" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO24" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP24" s="12" t="s">
+      <c r="AK24" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL24" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM24" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN24" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO24" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP24" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ24" s="8" t="s">
@@ -10612,32 +10612,32 @@
       <c r="U25" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V25" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W25" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X25" s="13"/>
-      <c r="Y25" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z25" s="14" t="s">
+      <c r="V25" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W25" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X25" s="12"/>
+      <c r="Y25" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z25" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA25" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB25" s="14" t="s">
+      <c r="AA25" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB25" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AC25" s="14" t="s">
+      <c r="AC25" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD25" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE25" s="15" t="s">
+      <c r="AD25" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE25" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF25" s="8" t="s">
@@ -10655,22 +10655,22 @@
       <c r="AJ25" s="8">
         <v>5</v>
       </c>
-      <c r="AK25" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL25" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM25" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN25" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO25" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP25" s="12" t="s">
+      <c r="AK25" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL25" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM25" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN25" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO25" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP25" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ25" s="8" t="s">
@@ -10859,32 +10859,32 @@
       <c r="U26" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V26" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W26" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X26" s="13"/>
-      <c r="Y26" s="14" t="s">
+      <c r="V26" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W26" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X26" s="12"/>
+      <c r="Y26" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z26" s="14" t="s">
+      <c r="Z26" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA26" s="14" t="s">
+      <c r="AA26" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB26" s="14" t="s">
+      <c r="AB26" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC26" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD26" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE26" s="15" t="s">
+      <c r="AC26" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD26" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE26" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF26" s="8">
@@ -10902,22 +10902,22 @@
       <c r="AJ26" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK26" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL26" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM26" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN26" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO26" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP26" s="12" t="s">
+      <c r="AK26" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL26" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM26" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN26" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO26" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP26" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ26" s="8" t="s">
@@ -11108,32 +11108,32 @@
       <c r="U27" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V27" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W27" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X27" s="13"/>
-      <c r="Y27" s="14" t="s">
+      <c r="V27" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W27" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z27" s="14" t="s">
+      <c r="Z27" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA27" s="14" t="s">
+      <c r="AA27" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB27" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC27" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD27" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE27" s="15" t="s">
+      <c r="AB27" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC27" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD27" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE27" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF27" s="8">
@@ -11151,22 +11151,22 @@
       <c r="AJ27" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK27" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL27" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM27" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN27" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO27" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP27" s="12" t="s">
+      <c r="AK27" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL27" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM27" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN27" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO27" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP27" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ27" s="8" t="s">
@@ -11357,32 +11357,32 @@
       <c r="U28" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V28" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W28" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X28" s="13"/>
-      <c r="Y28" s="14" t="s">
+      <c r="V28" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W28" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X28" s="12"/>
+      <c r="Y28" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z28" s="14" t="s">
+      <c r="Z28" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA28" s="14" t="s">
+      <c r="AA28" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB28" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC28" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD28" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE28" s="15" t="s">
+      <c r="AB28" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC28" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD28" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE28" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF28" s="8" t="s">
@@ -11400,22 +11400,22 @@
       <c r="AJ28" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK28" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL28" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM28" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN28" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO28" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP28" s="12" t="s">
+      <c r="AK28" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL28" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM28" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN28" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO28" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP28" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ28" s="8" t="s">
@@ -11608,32 +11608,32 @@
       <c r="U29" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V29" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W29" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z29" s="14" t="s">
+      <c r="V29" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W29" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z29" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AA29" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB29" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC29" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD29" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE29" s="15" t="s">
+      <c r="AA29" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB29" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC29" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD29" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE29" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF29" s="8" t="s">
@@ -11651,22 +11651,22 @@
       <c r="AJ29" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK29" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL29" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM29" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN29" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO29" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP29" s="12" t="s">
+      <c r="AK29" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL29" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM29" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN29" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO29" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP29" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ29" s="8" t="s">
@@ -11857,32 +11857,32 @@
       <c r="U30" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V30" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W30" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X30" s="13"/>
-      <c r="Y30" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z30" s="14" t="s">
+      <c r="V30" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W30" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z30" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA30" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB30" s="14" t="s">
+      <c r="AA30" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB30" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AC30" s="14" t="s">
+      <c r="AC30" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD30" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE30" s="15" t="s">
+      <c r="AD30" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE30" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF30" s="8" t="s">
@@ -11900,22 +11900,22 @@
       <c r="AJ30" s="8">
         <v>3</v>
       </c>
-      <c r="AK30" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL30" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM30" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN30" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO30" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP30" s="12" t="s">
+      <c r="AK30" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL30" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM30" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN30" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO30" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP30" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ30" s="8" t="s">
@@ -12106,32 +12106,32 @@
       <c r="U31" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V31" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W31" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X31" s="13"/>
-      <c r="Y31" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z31" s="14" t="s">
+      <c r="V31" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W31" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X31" s="12"/>
+      <c r="Y31" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z31" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA31" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB31" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC31" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD31" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE31" s="15" t="s">
+      <c r="AA31" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB31" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC31" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD31" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE31" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF31" s="8" t="s">
@@ -12149,22 +12149,22 @@
       <c r="AJ31" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK31" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL31" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM31" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN31" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO31" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP31" s="12" t="s">
+      <c r="AK31" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL31" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM31" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN31" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO31" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP31" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ31" s="8" t="s">
@@ -12355,32 +12355,32 @@
       <c r="U32" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V32" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W32" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X32" s="13"/>
-      <c r="Y32" s="14" t="s">
+      <c r="V32" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W32" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X32" s="12"/>
+      <c r="Y32" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z32" s="14" t="s">
+      <c r="Z32" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA32" s="14" t="s">
+      <c r="AA32" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB32" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC32" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD32" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE32" s="15" t="s">
+      <c r="AB32" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC32" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD32" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE32" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF32" s="8" t="s">
@@ -12398,22 +12398,22 @@
       <c r="AJ32" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK32" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL32" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM32" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN32" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO32" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP32" s="12" t="s">
+      <c r="AK32" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL32" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM32" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN32" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO32" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP32" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ32" s="8" t="s">
@@ -12608,32 +12608,32 @@
       <c r="U33" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V33" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W33" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X33" s="13"/>
-      <c r="Y33" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z33" s="14" t="s">
+      <c r="V33" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W33" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X33" s="12"/>
+      <c r="Y33" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z33" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA33" s="14" t="s">
+      <c r="AA33" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB33" s="14" t="s">
+      <c r="AB33" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC33" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD33" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE33" s="15" t="s">
+      <c r="AC33" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD33" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE33" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF33" s="8" t="s">
@@ -12651,22 +12651,22 @@
       <c r="AJ33" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK33" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL33" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM33" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN33" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO33" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP33" s="12" t="s">
+      <c r="AK33" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL33" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM33" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN33" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO33" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP33" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ33" s="8" t="s">
@@ -12859,32 +12859,32 @@
       <c r="U34" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V34" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W34" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X34" s="13"/>
-      <c r="Y34" s="14" t="s">
+      <c r="V34" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W34" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X34" s="12"/>
+      <c r="Y34" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z34" s="14" t="s">
+      <c r="Z34" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AA34" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB34" s="14" t="s">
+      <c r="AA34" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB34" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC34" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD34" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE34" s="15" t="s">
+      <c r="AC34" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD34" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE34" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF34" s="8">
@@ -12902,22 +12902,22 @@
       <c r="AJ34" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK34" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL34" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM34" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN34" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO34" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP34" s="12" t="s">
+      <c r="AK34" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL34" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM34" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN34" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO34" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP34" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ34" s="8" t="s">
@@ -13108,32 +13108,32 @@
       <c r="U35" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V35" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W35" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X35" s="13"/>
-      <c r="Y35" s="14" t="s">
+      <c r="V35" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W35" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X35" s="12"/>
+      <c r="Y35" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z35" s="14" t="s">
+      <c r="Z35" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA35" s="14" t="s">
+      <c r="AA35" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB35" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC35" s="14" t="s">
+      <c r="AB35" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC35" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD35" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE35" s="15" t="s">
+      <c r="AD35" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE35" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF35" s="8">
@@ -13151,22 +13151,22 @@
       <c r="AJ35" s="8">
         <v>2</v>
       </c>
-      <c r="AK35" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL35" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM35" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN35" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO35" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP35" s="12" t="s">
+      <c r="AK35" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL35" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM35" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN35" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO35" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP35" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ35" s="8" t="s">
@@ -13359,32 +13359,32 @@
       <c r="U36" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V36" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W36" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X36" s="13"/>
-      <c r="Y36" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z36" s="14" t="s">
+      <c r="V36" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W36" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X36" s="12"/>
+      <c r="Y36" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z36" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA36" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB36" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC36" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD36" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE36" s="15" t="s">
+      <c r="AA36" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB36" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC36" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD36" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE36" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF36" s="8" t="s">
@@ -13402,22 +13402,22 @@
       <c r="AJ36" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK36" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL36" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM36" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN36" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO36" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP36" s="12" t="s">
+      <c r="AK36" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL36" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM36" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN36" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO36" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP36" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ36" s="8" t="s">
@@ -13608,32 +13608,32 @@
       <c r="U37" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V37" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W37" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X37" s="13"/>
-      <c r="Y37" s="14" t="s">
+      <c r="V37" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W37" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X37" s="12"/>
+      <c r="Y37" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z37" s="14" t="s">
+      <c r="Z37" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA37" s="14" t="s">
+      <c r="AA37" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB37" s="14" t="s">
+      <c r="AB37" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC37" s="14" t="s">
+      <c r="AC37" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD37" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE37" s="15" t="s">
+      <c r="AD37" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE37" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF37" s="8">
@@ -13651,22 +13651,22 @@
       <c r="AJ37" s="8">
         <v>4</v>
       </c>
-      <c r="AK37" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL37" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM37" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN37" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO37" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP37" s="12" t="s">
+      <c r="AK37" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL37" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM37" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN37" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO37" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP37" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ37" s="8" t="s">
@@ -13859,32 +13859,32 @@
       <c r="U38" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V38" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W38" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X38" s="13"/>
-      <c r="Y38" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z38" s="14" t="s">
+      <c r="V38" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W38" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X38" s="12"/>
+      <c r="Y38" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z38" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA38" s="14" t="s">
+      <c r="AA38" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB38" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC38" s="14" t="s">
+      <c r="AB38" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC38" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD38" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE38" s="15" t="s">
+      <c r="AD38" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE38" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF38" s="8" t="s">
@@ -13902,22 +13902,22 @@
       <c r="AJ38" s="8">
         <v>3</v>
       </c>
-      <c r="AK38" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL38" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM38" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN38" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO38" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP38" s="12" t="s">
+      <c r="AK38" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL38" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM38" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN38" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO38" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP38" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ38" s="8" t="s">
@@ -14102,32 +14102,32 @@
       <c r="U39" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V39" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W39" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X39" s="13"/>
-      <c r="Y39" s="14" t="s">
+      <c r="V39" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W39" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X39" s="12"/>
+      <c r="Y39" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z39" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA39" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB39" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC39" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD39" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE39" s="15" t="s">
+      <c r="Z39" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA39" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB39" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC39" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD39" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE39" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF39" s="8" t="s">
@@ -14145,22 +14145,22 @@
       <c r="AJ39" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK39" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL39" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM39" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN39" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO39" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP39" s="12" t="s">
+      <c r="AK39" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL39" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM39" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN39" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO39" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP39" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ39" s="8" t="s">
@@ -14349,32 +14349,32 @@
       <c r="U40" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V40" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W40" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X40" s="13"/>
-      <c r="Y40" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z40" s="14" t="s">
+      <c r="V40" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W40" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X40" s="12"/>
+      <c r="Y40" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z40" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA40" s="14" t="s">
+      <c r="AA40" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB40" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC40" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD40" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE40" s="15" t="s">
+      <c r="AB40" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC40" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD40" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE40" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF40" s="8" t="s">
@@ -14392,22 +14392,22 @@
       <c r="AJ40" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK40" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL40" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM40" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN40" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO40" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP40" s="12" t="s">
+      <c r="AK40" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL40" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM40" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN40" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO40" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP40" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ40" s="8" t="s">
@@ -14592,32 +14592,32 @@
       <c r="U41" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V41" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W41" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X41" s="13"/>
-      <c r="Y41" s="14" t="s">
+      <c r="V41" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W41" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X41" s="12"/>
+      <c r="Y41" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z41" s="14" t="s">
+      <c r="Z41" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA41" s="14" t="s">
+      <c r="AA41" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB41" s="14" t="s">
+      <c r="AB41" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC41" s="14" t="s">
+      <c r="AC41" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD41" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE41" s="15" t="s">
+      <c r="AD41" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE41" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF41" s="8">
@@ -14635,22 +14635,22 @@
       <c r="AJ41" s="8">
         <v>3</v>
       </c>
-      <c r="AK41" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL41" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM41" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN41" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO41" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP41" s="12" t="s">
+      <c r="AK41" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL41" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM41" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN41" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO41" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP41" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ41" s="8" t="s">
@@ -14843,32 +14843,32 @@
       <c r="U42" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V42" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W42" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X42" s="13"/>
-      <c r="Y42" s="14" t="s">
+      <c r="V42" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W42" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X42" s="12"/>
+      <c r="Y42" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z42" s="14" t="s">
+      <c r="Z42" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA42" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB42" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC42" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD42" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE42" s="15" t="s">
+      <c r="AA42" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB42" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC42" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD42" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE42" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF42" s="8" t="s">
@@ -14886,22 +14886,22 @@
       <c r="AJ42" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK42" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL42" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM42" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN42" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO42" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP42" s="12" t="s">
+      <c r="AK42" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL42" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM42" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN42" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO42" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP42" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ42" s="8" t="s">
@@ -15090,32 +15090,32 @@
       <c r="U43" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V43" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W43" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X43" s="13"/>
-      <c r="Y43" s="14" t="s">
+      <c r="V43" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W43" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X43" s="12"/>
+      <c r="Y43" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z43" s="14" t="s">
+      <c r="Z43" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA43" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB43" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC43" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD43" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE43" s="15" t="s">
+      <c r="AA43" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB43" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC43" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD43" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE43" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF43" s="8">
@@ -15133,22 +15133,22 @@
       <c r="AJ43" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK43" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL43" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM43" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN43" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO43" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP43" s="12" t="s">
+      <c r="AK43" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL43" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM43" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN43" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO43" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP43" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ43" s="8" t="s">
@@ -15333,32 +15333,32 @@
       <c r="U44" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V44" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W44" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X44" s="13"/>
-      <c r="Y44" s="14" t="s">
+      <c r="V44" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W44" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X44" s="12"/>
+      <c r="Y44" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z44" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA44" s="14" t="s">
+      <c r="Z44" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA44" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB44" s="14" t="s">
+      <c r="AB44" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC44" s="14" t="s">
+      <c r="AC44" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD44" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE44" s="15" t="s">
+      <c r="AD44" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE44" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF44" s="8">
@@ -15376,22 +15376,22 @@
       <c r="AJ44" s="8">
         <v>2</v>
       </c>
-      <c r="AK44" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL44" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM44" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN44" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO44" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP44" s="12" t="s">
+      <c r="AK44" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL44" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM44" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN44" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO44" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP44" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ44" s="8" t="s">
@@ -15582,32 +15582,32 @@
       <c r="U45" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V45" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W45" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X45" s="13"/>
-      <c r="Y45" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z45" s="14" t="s">
+      <c r="V45" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W45" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X45" s="12"/>
+      <c r="Y45" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z45" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA45" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB45" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC45" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD45" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE45" s="15" t="s">
+      <c r="AA45" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB45" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC45" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD45" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE45" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF45" s="8" t="s">
@@ -15625,22 +15625,22 @@
       <c r="AJ45" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK45" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL45" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM45" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN45" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO45" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP45" s="12" t="s">
+      <c r="AK45" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL45" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM45" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN45" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO45" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP45" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ45" s="8" t="s">
@@ -15831,32 +15831,32 @@
       <c r="U46" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V46" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W46" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X46" s="13"/>
-      <c r="Y46" s="14" t="s">
+      <c r="V46" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W46" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X46" s="12"/>
+      <c r="Y46" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z46" s="14" t="s">
+      <c r="Z46" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA46" s="14" t="s">
+      <c r="AA46" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB46" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC46" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD46" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE46" s="15" t="s">
+      <c r="AB46" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC46" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD46" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE46" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF46" s="8">
@@ -15874,22 +15874,22 @@
       <c r="AJ46" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK46" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL46" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM46" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN46" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO46" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP46" s="12" t="s">
+      <c r="AK46" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL46" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM46" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN46" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO46" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP46" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ46" s="8" t="s">
@@ -16080,32 +16080,32 @@
       <c r="U47" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V47" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W47" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X47" s="13"/>
-      <c r="Y47" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z47" s="14" t="s">
+      <c r="V47" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W47" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X47" s="12"/>
+      <c r="Y47" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z47" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA47" s="14" t="s">
+      <c r="AA47" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB47" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC47" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD47" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE47" s="15" t="s">
+      <c r="AB47" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC47" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD47" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE47" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF47" s="8" t="s">
@@ -16123,22 +16123,22 @@
       <c r="AJ47" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK47" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL47" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM47" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN47" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO47" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP47" s="12" t="s">
+      <c r="AK47" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL47" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM47" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN47" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO47" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP47" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ47" s="8" t="s">
@@ -16331,32 +16331,32 @@
       <c r="U48" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V48" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W48" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X48" s="13"/>
-      <c r="Y48" s="14" t="s">
+      <c r="V48" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W48" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X48" s="12"/>
+      <c r="Y48" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z48" s="14" t="s">
+      <c r="Z48" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA48" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB48" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC48" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD48" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE48" s="15" t="s">
+      <c r="AA48" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB48" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC48" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD48" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE48" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF48" s="8" t="s">
@@ -16374,22 +16374,22 @@
       <c r="AJ48" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK48" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL48" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM48" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN48" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO48" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP48" s="12" t="s">
+      <c r="AK48" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL48" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM48" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN48" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO48" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP48" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ48" s="8" t="s">
@@ -16578,32 +16578,32 @@
       <c r="U49" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V49" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W49" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z49" s="14" t="s">
+      <c r="V49" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W49" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X49" s="12"/>
+      <c r="Y49" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z49" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA49" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB49" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC49" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD49" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE49" s="15" t="s">
+      <c r="AA49" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB49" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC49" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD49" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE49" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF49" s="8" t="s">
@@ -16621,22 +16621,22 @@
       <c r="AJ49" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK49" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL49" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM49" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN49" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO49" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP49" s="12" t="s">
+      <c r="AK49" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL49" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM49" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN49" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO49" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP49" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ49" s="8" t="s">
@@ -16827,32 +16827,32 @@
       <c r="U50" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V50" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W50" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X50" s="13"/>
-      <c r="Y50" s="14" t="s">
+      <c r="V50" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W50" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X50" s="12"/>
+      <c r="Y50" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z50" s="14" t="s">
+      <c r="Z50" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA50" s="14" t="s">
+      <c r="AA50" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB50" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC50" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD50" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE50" s="15" t="s">
+      <c r="AB50" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC50" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD50" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE50" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF50" s="8">
@@ -16870,22 +16870,22 @@
       <c r="AJ50" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK50" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL50" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM50" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN50" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO50" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP50" s="12" t="s">
+      <c r="AK50" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL50" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM50" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN50" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO50" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP50" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ50" s="8" t="s">
@@ -17076,32 +17076,32 @@
       <c r="U51" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V51" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W51" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z51" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA51" s="14" t="s">
+      <c r="V51" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W51" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X51" s="12"/>
+      <c r="Y51" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z51" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA51" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB51" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC51" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD51" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE51" s="15" t="s">
+      <c r="AB51" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC51" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD51" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE51" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF51" s="8" t="s">
@@ -17119,22 +17119,22 @@
       <c r="AJ51" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK51" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL51" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM51" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN51" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO51" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP51" s="12" t="s">
+      <c r="AK51" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL51" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM51" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN51" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO51" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP51" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ51" s="8" t="s">
@@ -17325,32 +17325,32 @@
       <c r="U52" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V52" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W52" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X52" s="13"/>
-      <c r="Y52" s="14" t="s">
+      <c r="V52" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W52" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X52" s="12"/>
+      <c r="Y52" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z52" s="14" t="s">
+      <c r="Z52" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA52" s="14" t="s">
+      <c r="AA52" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB52" s="14" t="s">
+      <c r="AB52" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AC52" s="14" t="s">
+      <c r="AC52" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AD52" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE52" s="15" t="s">
+      <c r="AD52" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE52" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF52" s="8" t="s">
@@ -17368,22 +17368,22 @@
       <c r="AJ52" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK52" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL52" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM52" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN52" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO52" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP52" s="12" t="s">
+      <c r="AK52" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL52" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM52" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN52" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO52" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP52" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ52" s="8" t="s">
@@ -17568,32 +17568,32 @@
       <c r="U53" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V53" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W53" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X53" s="13"/>
-      <c r="Y53" s="14" t="s">
+      <c r="V53" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W53" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X53" s="12"/>
+      <c r="Y53" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z53" s="14" t="s">
+      <c r="Z53" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA53" s="14" t="s">
+      <c r="AA53" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB53" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC53" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD53" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE53" s="15" t="s">
+      <c r="AB53" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC53" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD53" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE53" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF53" s="8">
@@ -17611,22 +17611,22 @@
       <c r="AJ53" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK53" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL53" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM53" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN53" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO53" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP53" s="12" t="s">
+      <c r="AK53" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL53" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM53" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN53" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO53" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP53" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ53" s="8" t="s">
@@ -17819,32 +17819,32 @@
       <c r="U54" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V54" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W54" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X54" s="13"/>
-      <c r="Y54" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z54" s="14" t="s">
+      <c r="V54" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W54" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X54" s="12"/>
+      <c r="Y54" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z54" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA54" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB54" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC54" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD54" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE54" s="15" t="s">
+      <c r="AA54" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB54" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC54" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD54" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE54" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF54" s="8" t="s">
@@ -17862,22 +17862,22 @@
       <c r="AJ54" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK54" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL54" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM54" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN54" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO54" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP54" s="12" t="s">
+      <c r="AK54" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL54" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM54" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN54" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO54" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP54" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ54" s="8" t="s">
@@ -18068,32 +18068,32 @@
       <c r="U55" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V55" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W55" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X55" s="13"/>
-      <c r="Y55" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z55" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA55" s="14" t="s">
+      <c r="V55" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W55" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X55" s="12"/>
+      <c r="Y55" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z55" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA55" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB55" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC55" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD55" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE55" s="15" t="s">
+      <c r="AB55" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC55" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD55" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE55" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF55" s="8" t="s">
@@ -18111,22 +18111,22 @@
       <c r="AJ55" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK55" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL55" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM55" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN55" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO55" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP55" s="12" t="s">
+      <c r="AK55" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL55" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM55" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN55" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO55" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP55" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ55" s="8" t="s">
@@ -18319,32 +18319,32 @@
       <c r="U56" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V56" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W56" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X56" s="13"/>
-      <c r="Y56" s="14" t="s">
+      <c r="V56" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W56" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X56" s="12"/>
+      <c r="Y56" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z56" s="14" t="s">
+      <c r="Z56" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA56" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB56" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC56" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD56" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE56" s="15" t="s">
+      <c r="AA56" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB56" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC56" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD56" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE56" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF56" s="8" t="s">
@@ -18362,22 +18362,22 @@
       <c r="AJ56" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK56" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL56" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM56" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN56" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO56" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP56" s="12" t="s">
+      <c r="AK56" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL56" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM56" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN56" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO56" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP56" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ56" s="8" t="s">
@@ -18566,32 +18566,32 @@
       <c r="U57" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V57" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W57" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X57" s="13"/>
-      <c r="Y57" s="14" t="s">
+      <c r="V57" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W57" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X57" s="12"/>
+      <c r="Y57" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z57" s="14" t="s">
+      <c r="Z57" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA57" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB57" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC57" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD57" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE57" s="15" t="s">
+      <c r="AA57" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB57" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC57" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD57" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE57" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF57" s="8">
@@ -18609,22 +18609,22 @@
       <c r="AJ57" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK57" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL57" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM57" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN57" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO57" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AP57" s="12" t="s">
+      <c r="AK57" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL57" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM57" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN57" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO57" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP57" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ57" s="8" t="s">
@@ -18815,32 +18815,32 @@
       <c r="U58" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V58" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W58" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X58" s="13"/>
-      <c r="Y58" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z58" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA58" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB58" s="14" t="s">
+      <c r="V58" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W58" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X58" s="12"/>
+      <c r="Y58" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z58" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA58" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB58" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC58" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD58" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE58" s="15" t="s">
+      <c r="AC58" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD58" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE58" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF58" s="8" t="s">
@@ -18858,22 +18858,22 @@
       <c r="AJ58" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK58" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL58" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM58" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN58" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO58" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP58" s="12" t="s">
+      <c r="AK58" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL58" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM58" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN58" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO58" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP58" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ58" s="8" t="s">
@@ -19064,32 +19064,32 @@
       <c r="U59" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V59" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W59" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X59" s="13"/>
-      <c r="Y59" s="14" t="s">
+      <c r="V59" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W59" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X59" s="12"/>
+      <c r="Y59" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z59" s="14" t="s">
+      <c r="Z59" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA59" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB59" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC59" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD59" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE59" s="15" t="s">
+      <c r="AA59" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB59" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC59" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD59" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE59" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF59" s="8">
@@ -19107,22 +19107,22 @@
       <c r="AJ59" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK59" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL59" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM59" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN59" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO59" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AP59" s="12" t="s">
+      <c r="AK59" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL59" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM59" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN59" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO59" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP59" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ59" s="8" t="s">
@@ -19311,32 +19311,32 @@
       <c r="U60" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V60" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W60" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X60" s="13"/>
-      <c r="Y60" s="14" t="s">
+      <c r="V60" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W60" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X60" s="12"/>
+      <c r="Y60" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z60" s="14" t="s">
+      <c r="Z60" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA60" s="14" t="s">
+      <c r="AA60" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB60" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC60" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD60" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE60" s="15" t="s">
+      <c r="AB60" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC60" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD60" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE60" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF60" s="8">
@@ -19354,22 +19354,22 @@
       <c r="AJ60" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK60" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL60" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM60" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN60" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO60" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP60" s="12" t="s">
+      <c r="AK60" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL60" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM60" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN60" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO60" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP60" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ60" s="8" t="s">
@@ -19558,32 +19558,32 @@
       <c r="U61" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V61" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W61" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X61" s="13"/>
-      <c r="Y61" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z61" s="14" t="s">
+      <c r="V61" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W61" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X61" s="12"/>
+      <c r="Y61" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z61" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA61" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB61" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC61" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD61" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE61" s="15" t="s">
+      <c r="AA61" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB61" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC61" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD61" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE61" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF61" s="8" t="s">
@@ -19601,22 +19601,22 @@
       <c r="AJ61" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK61" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL61" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM61" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN61" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO61" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP61" s="12" t="s">
+      <c r="AK61" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL61" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM61" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN61" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO61" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP61" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ61" s="8" t="s">
@@ -19805,32 +19805,32 @@
       <c r="U62" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V62" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W62" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X62" s="13"/>
-      <c r="Y62" s="14" t="s">
+      <c r="V62" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W62" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X62" s="12"/>
+      <c r="Y62" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z62" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA62" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB62" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC62" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD62" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE62" s="15" t="s">
+      <c r="Z62" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA62" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB62" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC62" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD62" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE62" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF62" s="8">
@@ -19848,22 +19848,22 @@
       <c r="AJ62" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK62" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL62" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM62" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN62" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO62" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP62" s="12" t="s">
+      <c r="AK62" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL62" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM62" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN62" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO62" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP62" s="11" t="s">
         <v>85</v>
       </c>
       <c r="AQ62" s="8" t="s">
@@ -20052,32 +20052,32 @@
       <c r="U63" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V63" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W63" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X63" s="13"/>
-      <c r="Y63" s="14" t="s">
+      <c r="V63" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W63" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X63" s="12"/>
+      <c r="Y63" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z63" s="14" t="s">
+      <c r="Z63" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA63" s="14" t="s">
+      <c r="AA63" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB63" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC63" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD63" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE63" s="15" t="s">
+      <c r="AB63" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC63" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD63" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE63" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF63" s="8" t="s">
@@ -20095,22 +20095,22 @@
       <c r="AJ63" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK63" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL63" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM63" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN63" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO63" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP63" s="12" t="s">
+      <c r="AK63" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL63" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM63" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN63" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO63" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP63" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ63" s="8" t="s">
@@ -20305,32 +20305,32 @@
       <c r="U64" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V64" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W64" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X64" s="13"/>
-      <c r="Y64" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z64" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA64" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB64" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC64" s="14" t="s">
+      <c r="V64" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W64" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X64" s="12"/>
+      <c r="Y64" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z64" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA64" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB64" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC64" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD64" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE64" s="15" t="s">
+      <c r="AD64" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE64" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF64" s="8" t="s">
@@ -20348,22 +20348,22 @@
       <c r="AJ64" s="8">
         <v>4</v>
       </c>
-      <c r="AK64" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL64" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM64" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN64" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO64" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP64" s="12" t="s">
+      <c r="AK64" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL64" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM64" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN64" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO64" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP64" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ64" s="8" t="s">
@@ -20554,32 +20554,32 @@
       <c r="U65" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V65" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W65" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X65" s="13"/>
-      <c r="Y65" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z65" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA65" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB65" s="14" t="s">
+      <c r="V65" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W65" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X65" s="12"/>
+      <c r="Y65" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z65" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA65" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB65" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC65" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD65" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE65" s="15" t="s">
+      <c r="AC65" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD65" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE65" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF65" s="8" t="s">
@@ -20597,22 +20597,22 @@
       <c r="AJ65" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK65" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL65" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM65" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN65" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO65" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP65" s="12" t="s">
+      <c r="AK65" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL65" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM65" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN65" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO65" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP65" s="11" t="s">
         <v>85</v>
       </c>
       <c r="AQ65" s="8" t="s">
@@ -20801,32 +20801,32 @@
       <c r="U66" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V66" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W66" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X66" s="13"/>
-      <c r="Y66" s="14" t="s">
+      <c r="V66" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W66" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X66" s="12"/>
+      <c r="Y66" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z66" s="14" t="s">
+      <c r="Z66" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA66" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB66" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC66" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD66" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE66" s="15" t="s">
+      <c r="AA66" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB66" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC66" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD66" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE66" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF66" s="8">
@@ -20844,22 +20844,22 @@
       <c r="AJ66" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK66" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL66" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM66" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN66" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO66" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP66" s="12" t="s">
+      <c r="AK66" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL66" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM66" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN66" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO66" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP66" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ66" s="8" t="s">
@@ -21044,32 +21044,32 @@
       <c r="U67" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V67" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W67" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X67" s="13"/>
-      <c r="Y67" s="14" t="s">
+      <c r="V67" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W67" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X67" s="12"/>
+      <c r="Y67" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z67" s="14" t="s">
+      <c r="Z67" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA67" s="14" t="s">
+      <c r="AA67" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB67" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC67" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD67" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE67" s="15" t="s">
+      <c r="AB67" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC67" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD67" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE67" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF67" s="8" t="s">
@@ -21087,22 +21087,22 @@
       <c r="AJ67" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK67" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL67" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM67" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN67" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO67" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP67" s="12" t="s">
+      <c r="AK67" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL67" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM67" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN67" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO67" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP67" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ67" s="8" t="s">
@@ -21293,32 +21293,32 @@
       <c r="U68" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V68" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W68" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X68" s="13"/>
-      <c r="Y68" s="14" t="s">
+      <c r="V68" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W68" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X68" s="12"/>
+      <c r="Y68" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z68" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA68" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB68" s="14" t="s">
+      <c r="Z68" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA68" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB68" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AC68" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD68" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE68" s="15" t="s">
+      <c r="AC68" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD68" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE68" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF68" s="8" t="s">
@@ -21336,22 +21336,22 @@
       <c r="AJ68" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK68" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL68" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM68" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN68" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO68" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP68" s="12" t="s">
+      <c r="AK68" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL68" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM68" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN68" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO68" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP68" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ68" s="8" t="s">
@@ -21538,32 +21538,32 @@
       <c r="U69" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V69" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W69" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X69" s="13"/>
-      <c r="Y69" s="14" t="s">
+      <c r="V69" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W69" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X69" s="12"/>
+      <c r="Y69" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z69" s="14" t="s">
+      <c r="Z69" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA69" s="14" t="s">
+      <c r="AA69" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB69" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC69" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD69" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE69" s="15" t="s">
+      <c r="AB69" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC69" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD69" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE69" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF69" s="8" t="s">
@@ -21581,22 +21581,22 @@
       <c r="AJ69" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK69" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL69" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM69" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN69" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO69" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP69" s="12" t="s">
+      <c r="AK69" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL69" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM69" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN69" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO69" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP69" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ69" s="8" t="s">
@@ -21781,32 +21781,32 @@
       <c r="U70" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V70" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W70" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X70" s="13"/>
-      <c r="Y70" s="14" t="s">
+      <c r="V70" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W70" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X70" s="12"/>
+      <c r="Y70" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z70" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA70" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB70" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC70" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD70" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE70" s="15" t="s">
+      <c r="Z70" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA70" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB70" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC70" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD70" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE70" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF70" s="8" t="s">
@@ -21824,22 +21824,22 @@
       <c r="AJ70" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK70" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL70" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM70" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN70" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO70" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP70" s="12" t="s">
+      <c r="AK70" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL70" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM70" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN70" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO70" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP70" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ70" s="8" t="s">
@@ -22030,32 +22030,32 @@
       <c r="U71" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V71" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W71" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X71" s="13"/>
-      <c r="Y71" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z71" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA71" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB71" s="14" t="s">
+      <c r="V71" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W71" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X71" s="12"/>
+      <c r="Y71" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z71" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA71" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB71" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AC71" s="14" t="s">
+      <c r="AC71" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD71" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE71" s="15" t="s">
+      <c r="AD71" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE71" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF71" s="8" t="s">
@@ -22073,22 +22073,22 @@
       <c r="AJ71" s="8">
         <v>2</v>
       </c>
-      <c r="AK71" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL71" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM71" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN71" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO71" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP71" s="12" t="s">
+      <c r="AK71" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL71" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM71" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN71" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO71" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP71" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ71" s="8" t="s">
@@ -22277,32 +22277,32 @@
       <c r="U72" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V72" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W72" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X72" s="13"/>
-      <c r="Y72" s="14" t="s">
+      <c r="V72" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W72" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X72" s="12"/>
+      <c r="Y72" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z72" s="14" t="s">
+      <c r="Z72" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA72" s="14" t="s">
+      <c r="AA72" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB72" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC72" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD72" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE72" s="15" t="s">
+      <c r="AB72" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC72" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD72" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE72" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF72" s="8">
@@ -22320,22 +22320,22 @@
       <c r="AJ72" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK72" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL72" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM72" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN72" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO72" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP72" s="12" t="s">
+      <c r="AK72" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL72" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM72" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN72" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO72" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP72" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ72" s="8" t="s">
@@ -22526,32 +22526,32 @@
       <c r="U73" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V73" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W73" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X73" s="13"/>
-      <c r="Y73" s="14" t="s">
+      <c r="V73" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W73" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X73" s="12"/>
+      <c r="Y73" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z73" s="14" t="s">
+      <c r="Z73" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA73" s="14" t="s">
+      <c r="AA73" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB73" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC73" s="14" t="s">
+      <c r="AB73" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC73" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AD73" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE73" s="15" t="s">
+      <c r="AD73" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE73" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF73" s="8" t="s">
@@ -22569,22 +22569,22 @@
       <c r="AJ73" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK73" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL73" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM73" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN73" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO73" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP73" s="12" t="s">
+      <c r="AK73" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL73" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM73" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN73" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO73" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP73" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ73" s="8" t="s">
@@ -22773,32 +22773,32 @@
       <c r="U74" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V74" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W74" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X74" s="13"/>
-      <c r="Y74" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z74" s="14" t="s">
+      <c r="V74" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W74" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X74" s="12"/>
+      <c r="Y74" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z74" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA74" s="14" t="s">
+      <c r="AA74" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB74" s="14" t="s">
+      <c r="AB74" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC74" s="14" t="s">
+      <c r="AC74" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD74" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE74" s="15" t="s">
+      <c r="AD74" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE74" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF74" s="8" t="s">
@@ -22816,22 +22816,22 @@
       <c r="AJ74" s="8">
         <v>3</v>
       </c>
-      <c r="AK74" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL74" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM74" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN74" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO74" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP74" s="12" t="s">
+      <c r="AK74" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL74" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM74" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN74" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO74" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP74" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ74" s="8" t="s">
@@ -23022,32 +23022,32 @@
       <c r="U75" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V75" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W75" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X75" s="13"/>
-      <c r="Y75" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z75" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA75" s="14" t="s">
+      <c r="V75" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W75" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X75" s="12"/>
+      <c r="Y75" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z75" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA75" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB75" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC75" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD75" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE75" s="15" t="s">
+      <c r="AB75" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC75" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD75" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE75" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF75" s="8" t="s">
@@ -23065,22 +23065,22 @@
       <c r="AJ75" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK75" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL75" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM75" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN75" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO75" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP75" s="12" t="s">
+      <c r="AK75" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL75" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM75" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN75" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO75" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP75" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ75" s="8" t="s">
@@ -23267,32 +23267,32 @@
       <c r="U76" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V76" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W76" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X76" s="13"/>
-      <c r="Y76" s="14" t="s">
+      <c r="V76" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W76" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X76" s="12"/>
+      <c r="Y76" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z76" s="14" t="s">
+      <c r="Z76" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA76" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB76" s="14" t="s">
+      <c r="AA76" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB76" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AC76" s="14" t="s">
+      <c r="AC76" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD76" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE76" s="15" t="s">
+      <c r="AD76" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE76" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF76" s="8">
@@ -23310,22 +23310,22 @@
       <c r="AJ76" s="8">
         <v>10</v>
       </c>
-      <c r="AK76" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL76" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM76" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN76" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO76" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP76" s="12" t="s">
+      <c r="AK76" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL76" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM76" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN76" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO76" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP76" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ76" s="8" t="s">
@@ -23518,32 +23518,32 @@
       <c r="U77" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V77" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W77" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X77" s="13"/>
-      <c r="Y77" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z77" s="14" t="s">
+      <c r="V77" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W77" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X77" s="12"/>
+      <c r="Y77" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z77" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA77" s="14" t="s">
+      <c r="AA77" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB77" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC77" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD77" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE77" s="15" t="s">
+      <c r="AB77" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC77" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD77" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE77" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF77" s="8" t="s">
@@ -23561,22 +23561,22 @@
       <c r="AJ77" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK77" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL77" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM77" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN77" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO77" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP77" s="12" t="s">
+      <c r="AK77" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL77" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM77" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN77" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO77" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP77" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ77" s="8" t="s">
@@ -23767,32 +23767,32 @@
       <c r="U78" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V78" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W78" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X78" s="13"/>
-      <c r="Y78" s="14" t="s">
+      <c r="V78" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W78" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X78" s="12"/>
+      <c r="Y78" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z78" s="14" t="s">
+      <c r="Z78" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA78" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB78" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC78" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD78" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE78" s="15" t="s">
+      <c r="AA78" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB78" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC78" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD78" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE78" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF78" s="8" t="s">
@@ -23810,22 +23810,22 @@
       <c r="AJ78" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK78" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL78" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM78" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN78" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO78" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP78" s="12" t="s">
+      <c r="AK78" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL78" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM78" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN78" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO78" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP78" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ78" s="8" t="s">
@@ -24016,32 +24016,32 @@
       <c r="U79" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V79" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W79" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X79" s="13"/>
-      <c r="Y79" s="14" t="s">
+      <c r="V79" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W79" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X79" s="12"/>
+      <c r="Y79" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z79" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA79" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB79" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC79" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD79" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE79" s="15" t="s">
+      <c r="Z79" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA79" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB79" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC79" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD79" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE79" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF79" s="8">
@@ -24059,22 +24059,22 @@
       <c r="AJ79" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK79" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL79" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM79" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN79" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO79" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP79" s="12" t="s">
+      <c r="AK79" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL79" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM79" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN79" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO79" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP79" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ79" s="8" t="s">
@@ -24265,32 +24265,32 @@
       <c r="U80" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V80" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W80" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X80" s="13"/>
-      <c r="Y80" s="14" t="s">
+      <c r="V80" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W80" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X80" s="12"/>
+      <c r="Y80" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z80" s="14" t="s">
+      <c r="Z80" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA80" s="14" t="s">
+      <c r="AA80" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB80" s="14" t="s">
+      <c r="AB80" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC80" s="14" t="s">
+      <c r="AC80" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AD80" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE80" s="15" t="s">
+      <c r="AD80" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE80" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF80" s="8" t="s">
@@ -24308,22 +24308,22 @@
       <c r="AJ80" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK80" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL80" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM80" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN80" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO80" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP80" s="12" t="s">
+      <c r="AK80" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL80" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM80" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN80" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO80" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP80" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ80" s="8" t="s">
@@ -24512,32 +24512,32 @@
       <c r="U81" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V81" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W81" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X81" s="13"/>
-      <c r="Y81" s="14" t="s">
+      <c r="V81" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W81" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X81" s="12"/>
+      <c r="Y81" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z81" s="14" t="s">
+      <c r="Z81" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA81" s="14" t="s">
+      <c r="AA81" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB81" s="14" t="s">
+      <c r="AB81" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC81" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD81" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE81" s="15" t="s">
+      <c r="AC81" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD81" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE81" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF81" s="8">
@@ -24555,22 +24555,22 @@
       <c r="AJ81" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK81" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL81" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM81" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN81" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO81" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP81" s="12" t="s">
+      <c r="AK81" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL81" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM81" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN81" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO81" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP81" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ81" s="8" t="s">
@@ -24761,32 +24761,32 @@
       <c r="U82" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V82" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W82" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X82" s="13"/>
-      <c r="Y82" s="14" t="s">
+      <c r="V82" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W82" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X82" s="12"/>
+      <c r="Y82" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z82" s="14" t="s">
+      <c r="Z82" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA82" s="14" t="s">
+      <c r="AA82" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB82" s="14" t="s">
+      <c r="AB82" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC82" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD82" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE82" s="15" t="s">
+      <c r="AC82" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD82" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE82" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF82" s="8">
@@ -24804,22 +24804,22 @@
       <c r="AJ82" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK82" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL82" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM82" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN82" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO82" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP82" s="12" t="s">
+      <c r="AK82" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL82" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM82" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN82" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO82" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP82" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ82" s="8" t="s">
@@ -25008,32 +25008,32 @@
       <c r="U83" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V83" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W83" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X83" s="13"/>
-      <c r="Y83" s="14" t="s">
+      <c r="V83" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W83" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X83" s="12"/>
+      <c r="Y83" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z83" s="14" t="s">
+      <c r="Z83" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA83" s="14" t="s">
+      <c r="AA83" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB83" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC83" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD83" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE83" s="15" t="s">
+      <c r="AB83" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC83" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD83" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE83" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF83" s="8" t="s">
@@ -25051,22 +25051,22 @@
       <c r="AJ83" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK83" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL83" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM83" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN83" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO83" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP83" s="12" t="s">
+      <c r="AK83" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL83" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM83" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN83" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO83" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP83" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ83" s="8" t="s">
@@ -25259,32 +25259,32 @@
       <c r="U84" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V84" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W84" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X84" s="13"/>
-      <c r="Y84" s="14" t="s">
+      <c r="V84" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W84" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X84" s="12"/>
+      <c r="Y84" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z84" s="14" t="s">
+      <c r="Z84" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA84" s="14" t="s">
+      <c r="AA84" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB84" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC84" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD84" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE84" s="15" t="s">
+      <c r="AB84" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC84" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD84" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE84" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF84" s="8" t="s">
@@ -25302,22 +25302,22 @@
       <c r="AJ84" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK84" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL84" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM84" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN84" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO84" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP84" s="12" t="s">
+      <c r="AK84" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL84" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM84" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN84" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO84" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP84" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ84" s="8" t="s">
@@ -25508,32 +25508,32 @@
       <c r="U85" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V85" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W85" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X85" s="13"/>
-      <c r="Y85" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z85" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA85" s="14" t="s">
+      <c r="V85" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W85" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X85" s="12"/>
+      <c r="Y85" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z85" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA85" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB85" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC85" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD85" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE85" s="15" t="s">
+      <c r="AB85" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC85" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD85" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE85" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF85" s="8" t="s">
@@ -25551,22 +25551,22 @@
       <c r="AJ85" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK85" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL85" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM85" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN85" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO85" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP85" s="12" t="s">
+      <c r="AK85" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL85" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM85" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN85" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO85" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP85" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ85" s="8" t="s">
@@ -25757,32 +25757,32 @@
       <c r="U86" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V86" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W86" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X86" s="13"/>
-      <c r="Y86" s="14" t="s">
+      <c r="V86" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W86" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X86" s="12"/>
+      <c r="Y86" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z86" s="14" t="s">
+      <c r="Z86" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA86" s="14" t="s">
+      <c r="AA86" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB86" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC86" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD86" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE86" s="15" t="s">
+      <c r="AB86" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC86" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD86" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE86" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF86" s="8">
@@ -25800,22 +25800,22 @@
       <c r="AJ86" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK86" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL86" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM86" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN86" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO86" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP86" s="12" t="s">
+      <c r="AK86" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL86" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM86" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN86" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO86" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP86" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ86" s="8" t="s">
@@ -26006,32 +26006,32 @@
       <c r="U87" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V87" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W87" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X87" s="13"/>
-      <c r="Y87" s="14" t="s">
+      <c r="V87" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W87" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X87" s="12"/>
+      <c r="Y87" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z87" s="14" t="s">
+      <c r="Z87" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA87" s="14" t="s">
+      <c r="AA87" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB87" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC87" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD87" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE87" s="15" t="s">
+      <c r="AB87" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC87" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD87" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE87" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF87" s="8" t="s">
@@ -26049,22 +26049,22 @@
       <c r="AJ87" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK87" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL87" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM87" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN87" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO87" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP87" s="12" t="s">
+      <c r="AK87" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL87" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM87" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN87" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO87" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP87" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ87" s="8" t="s">
@@ -26249,32 +26249,32 @@
       <c r="U88" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V88" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W88" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X88" s="13"/>
-      <c r="Y88" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z88" s="14" t="s">
+      <c r="V88" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W88" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X88" s="12"/>
+      <c r="Y88" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z88" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA88" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB88" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC88" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD88" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE88" s="15" t="s">
+      <c r="AA88" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB88" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC88" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD88" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE88" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF88" s="8" t="s">
@@ -26292,22 +26292,22 @@
       <c r="AJ88" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK88" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL88" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM88" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN88" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO88" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP88" s="12" t="s">
+      <c r="AK88" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL88" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM88" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN88" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO88" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP88" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ88" s="8" t="s">
@@ -26498,32 +26498,32 @@
       <c r="U89" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V89" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W89" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="X89" s="13"/>
-      <c r="Y89" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z89" s="14" t="s">
+      <c r="V89" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W89" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X89" s="12"/>
+      <c r="Y89" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z89" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA89" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB89" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC89" s="14" t="s">
+      <c r="AA89" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB89" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC89" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AD89" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE89" s="15" t="s">
+      <c r="AD89" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE89" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AF89" s="8" t="s">
@@ -26541,22 +26541,22 @@
       <c r="AJ89" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK89" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL89" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM89" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN89" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO89" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP89" s="12" t="s">
+      <c r="AK89" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL89" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM89" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN89" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO89" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP89" s="11" t="s">
         <v>90</v>
       </c>
       <c r="AQ89" s="8" t="s">
@@ -26747,32 +26747,32 @@
       <c r="U90" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V90" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="W90" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="X90" s="13"/>
-      <c r="Y90" s="14" t="s">
+      <c r="V90" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="W90" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="X90" s="12"/>
+      <c r="Y90" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z90" s="14" t="s">
+      <c r="Z90" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AA90" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB90" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC90" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD90" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE90" s="15" t="s">
+      <c r="AA90" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB90" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC90" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD90" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE90" s="14" t="s">
         <v>108</v>
       </c>
       <c r="AF90" s="8" t="s">
@@ -26790,22 +26790,22 @@
       <c r="AJ90" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK90" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AL90" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM90" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN90" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO90" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP90" s="15" t="s">
+      <c r="AK90" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL90" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM90" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN90" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO90" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP90" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AQ90" s="8" t="s">
@@ -26996,32 +26996,32 @@
       <c r="U91" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V91" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="W91" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="X91" s="13"/>
-      <c r="Y91" s="14" t="s">
+      <c r="V91" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="W91" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="X91" s="12"/>
+      <c r="Y91" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z91" s="14" t="s">
+      <c r="Z91" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA91" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB91" s="14" t="s">
+      <c r="AA91" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB91" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC91" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD91" s="15" t="s">
+      <c r="AC91" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD91" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="AE91" s="15" t="s">
+      <c r="AE91" s="14" t="s">
         <v>92</v>
       </c>
       <c r="AF91" s="8">
@@ -27039,22 +27039,22 @@
       <c r="AJ91" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK91" s="12">
+      <c r="AK91" s="11">
         <v>2</v>
       </c>
-      <c r="AL91" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM91" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN91" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO91" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP91" s="15" t="s">
+      <c r="AL91" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM91" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN91" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO91" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP91" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AQ91" s="8" t="s">
@@ -27245,32 +27245,32 @@
       <c r="U92" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V92" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="W92" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="X92" s="13"/>
-      <c r="Y92" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z92" s="14" t="s">
+      <c r="V92" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="W92" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="X92" s="12"/>
+      <c r="Y92" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z92" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA92" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB92" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC92" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD92" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE92" s="15" t="s">
+      <c r="AA92" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB92" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC92" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD92" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE92" s="14" t="s">
         <v>93</v>
       </c>
       <c r="AF92" s="8" t="s">
@@ -27288,22 +27288,22 @@
       <c r="AJ92" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK92" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AL92" s="12">
+      <c r="AK92" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL92" s="11">
         <v>4</v>
       </c>
-      <c r="AM92" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN92" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO92" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP92" s="15" t="s">
+      <c r="AM92" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN92" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO92" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP92" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AQ92" s="8" t="s">
@@ -27492,32 +27492,32 @@
       <c r="U93" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V93" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="W93" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="X93" s="13"/>
-      <c r="Y93" s="14" t="s">
+      <c r="V93" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="W93" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="X93" s="12"/>
+      <c r="Y93" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z93" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA93" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB93" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC93" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD93" s="15" t="s">
+      <c r="Z93" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA93" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB93" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC93" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD93" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="AE93" s="15" t="s">
+      <c r="AE93" s="14" t="s">
         <v>108</v>
       </c>
       <c r="AF93" s="8">
@@ -27535,22 +27535,22 @@
       <c r="AJ93" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK93" s="12">
+      <c r="AK93" s="11">
         <v>5</v>
       </c>
-      <c r="AL93" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM93" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN93" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO93" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP93" s="15" t="s">
+      <c r="AL93" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM93" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN93" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO93" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP93" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AQ93" s="8" t="s">
@@ -27741,32 +27741,32 @@
       <c r="U94" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V94" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="W94" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="X94" s="13"/>
-      <c r="Y94" s="14" t="s">
+      <c r="V94" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="W94" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="X94" s="12"/>
+      <c r="Y94" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z94" s="14" t="s">
+      <c r="Z94" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA94" s="14" t="s">
+      <c r="AA94" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB94" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC94" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD94" s="15" t="s">
+      <c r="AB94" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC94" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD94" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="AE94" s="15" t="s">
+      <c r="AE94" s="14" t="s">
         <v>93</v>
       </c>
       <c r="AF94" s="8">
@@ -27784,22 +27784,22 @@
       <c r="AJ94" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK94" s="12">
+      <c r="AK94" s="11">
         <v>6</v>
       </c>
-      <c r="AL94" s="12">
+      <c r="AL94" s="11">
         <v>6</v>
       </c>
-      <c r="AM94" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN94" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO94" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP94" s="15" t="s">
+      <c r="AM94" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN94" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO94" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP94" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AQ94" s="8" t="s">
@@ -27984,32 +27984,32 @@
       <c r="U95" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V95" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="W95" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="X95" s="13"/>
-      <c r="Y95" s="14" t="s">
+      <c r="V95" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="W95" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="X95" s="12"/>
+      <c r="Y95" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z95" s="14" t="s">
+      <c r="Z95" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA95" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB95" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC95" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD95" s="15" t="s">
+      <c r="AA95" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB95" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC95" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD95" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="AE95" s="15" t="s">
+      <c r="AE95" s="14" t="s">
         <v>93</v>
       </c>
       <c r="AF95" s="8">
@@ -28027,22 +28027,22 @@
       <c r="AJ95" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK95" s="12">
+      <c r="AK95" s="11">
         <v>3</v>
       </c>
-      <c r="AL95" s="12">
+      <c r="AL95" s="11">
         <v>2</v>
       </c>
-      <c r="AM95" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN95" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO95" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP95" s="15" t="s">
+      <c r="AM95" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN95" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO95" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP95" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AQ95" s="8" t="s">
@@ -28227,32 +28227,32 @@
       <c r="U96" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V96" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="W96" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="X96" s="13"/>
-      <c r="Y96" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z96" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA96" s="14" t="s">
+      <c r="V96" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="W96" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="X96" s="12"/>
+      <c r="Y96" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z96" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA96" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB96" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC96" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD96" s="15" t="s">
+      <c r="AB96" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC96" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD96" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="AE96" s="15" t="s">
+      <c r="AE96" s="14" t="s">
         <v>92</v>
       </c>
       <c r="AF96" s="8" t="s">
@@ -28270,22 +28270,22 @@
       <c r="AJ96" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK96" s="12">
+      <c r="AK96" s="11">
         <v>2</v>
       </c>
-      <c r="AL96" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM96" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN96" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO96" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP96" s="15" t="s">
+      <c r="AL96" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM96" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN96" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO96" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP96" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AQ96" s="8" t="s">
@@ -28474,32 +28474,32 @@
       <c r="U97" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V97" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="W97" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="X97" s="13"/>
-      <c r="Y97" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z97" s="14" t="s">
+      <c r="V97" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="W97" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="X97" s="12"/>
+      <c r="Y97" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z97" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA97" s="14" t="s">
+      <c r="AA97" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB97" s="14" t="s">
+      <c r="AB97" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC97" s="14" t="s">
+      <c r="AC97" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD97" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE97" s="15" t="s">
+      <c r="AD97" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE97" s="14" t="s">
         <v>92</v>
       </c>
       <c r="AF97" s="8" t="s">
@@ -28517,22 +28517,22 @@
       <c r="AJ97" s="8">
         <v>3</v>
       </c>
-      <c r="AK97" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AL97" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM97" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN97" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO97" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP97" s="15" t="s">
+      <c r="AK97" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL97" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM97" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN97" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO97" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP97" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AQ97" s="8" t="s">
@@ -28723,34 +28723,34 @@
       <c r="U98" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="V98" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="W98" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="X98" s="13" t="s">
+      <c r="V98" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="W98" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="X98" s="12" t="s">
         <v>548</v>
       </c>
-      <c r="Y98" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z98" s="14" t="s">
+      <c r="Y98" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z98" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA98" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB98" s="14" t="s">
+      <c r="AA98" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB98" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AC98" s="14" t="s">
+      <c r="AC98" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AD98" s="15" t="s">
+      <c r="AD98" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="AE98" s="15" t="s">
+      <c r="AE98" s="14" t="s">
         <v>93</v>
       </c>
       <c r="AF98" s="8" t="s">
@@ -28768,22 +28768,22 @@
       <c r="AJ98" s="8">
         <v>3</v>
       </c>
-      <c r="AK98" s="12">
+      <c r="AK98" s="11">
         <v>4</v>
       </c>
-      <c r="AL98" s="12">
+      <c r="AL98" s="11">
         <v>4</v>
       </c>
-      <c r="AM98" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN98" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO98" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP98" s="15" t="s">
+      <c r="AM98" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN98" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO98" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP98" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AQ98" s="8" t="s">
@@ -28976,32 +28976,32 @@
       <c r="U99" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V99" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="W99" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="X99" s="13"/>
-      <c r="Y99" s="14" t="s">
+      <c r="V99" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="W99" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="X99" s="12"/>
+      <c r="Y99" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z99" s="14" t="s">
+      <c r="Z99" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AA99" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB99" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC99" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD99" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE99" s="15" t="s">
+      <c r="AA99" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB99" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC99" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD99" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE99" s="14" t="s">
         <v>92</v>
       </c>
       <c r="AF99" s="8">
@@ -29019,22 +29019,22 @@
       <c r="AJ99" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK99" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AL99" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM99" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN99" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO99" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP99" s="15" t="s">
+      <c r="AK99" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL99" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM99" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN99" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO99" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP99" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AQ99" s="8" t="s">
@@ -29229,32 +29229,32 @@
       <c r="U100" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V100" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="W100" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="X100" s="13"/>
-      <c r="Y100" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z100" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA100" s="14" t="s">
+      <c r="V100" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="W100" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="X100" s="12"/>
+      <c r="Y100" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z100" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA100" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB100" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC100" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD100" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE100" s="15" t="s">
+      <c r="AB100" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC100" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD100" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE100" s="14" t="s">
         <v>108</v>
       </c>
       <c r="AF100" s="8" t="s">
@@ -29272,22 +29272,22 @@
       <c r="AJ100" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK100" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AL100" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM100" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN100" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO100" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP100" s="15" t="s">
+      <c r="AK100" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL100" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM100" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN100" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO100" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP100" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AQ100" s="8" t="s">
@@ -29478,32 +29478,32 @@
       <c r="U101" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="V101" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="W101" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="X101" s="13"/>
-      <c r="Y101" s="14" t="s">
+      <c r="V101" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="W101" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="X101" s="12"/>
+      <c r="Y101" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z101" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA101" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB101" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC101" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD101" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE101" s="15" t="s">
+      <c r="Z101" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA101" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB101" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC101" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD101" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE101" s="14" t="s">
         <v>108</v>
       </c>
       <c r="AF101" s="8" t="s">
@@ -29521,22 +29521,22 @@
       <c r="AJ101" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK101" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AL101" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM101" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN101" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO101" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP101" s="15" t="s">
+      <c r="AK101" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL101" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM101" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN101" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO101" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP101" s="14" t="s">
         <v>91</v>
       </c>
       <c r="AQ101" s="8" t="s">
